--- a/Results.xlsx
+++ b/Results.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://entuedu-my.sharepoint.com/personal/wwong029_e_ntu_edu_sg/Documents/24S2/Neural Network and Deep Learning/Project/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\work\gender classification\Neural-Networks-and-Deep-Learning-Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C7B92A60-B2AB-4B8B-9A13-A556E6C92F22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{418D2A24-AFD9-43B2-A822-1109DD57565A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{443E6BF5-3B8D-4A17-A50D-7ACF8BB371E2}"/>
   </bookViews>
@@ -112,11 +112,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -126,9 +127,7 @@
       <numFmt numFmtId="14" formatCode="0.00%"/>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="14" formatCode="0.00%"/>
@@ -137,7 +136,9 @@
       <numFmt numFmtId="14" formatCode="0.00%"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <font>
+        <b/>
+      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -156,10 +157,10 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F5EAEC6E-5447-4E36-8D59-42E3E6DAA083}" name="Table2" displayName="Table2" ref="A1:E6" totalsRowShown="0">
   <autoFilter ref="A1:E6" xr:uid="{F5EAEC6E-5447-4E36-8D59-42E3E6DAA083}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{4DADEE15-8A9C-4261-AFBB-FCC237FBFF32}" name="Model\Training data size" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{2CDC2B5A-DEA7-4603-8850-3897F2CDF776}" name="4000" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{5060743F-C095-4F0A-96EC-4EF75F791B0C}" name="8000" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{2F8F5957-488C-4C0E-BA55-0DA7501484F9}" name="12000" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{4DADEE15-8A9C-4261-AFBB-FCC237FBFF32}" name="Model\Training data size" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{2CDC2B5A-DEA7-4603-8850-3897F2CDF776}" name="4000" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{5060743F-C095-4F0A-96EC-4EF75F791B0C}" name="8000" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{2F8F5957-488C-4C0E-BA55-0DA7501484F9}" name="12000" dataDxfId="1"/>
     <tableColumn id="6" xr3:uid="{E0A3210C-CFA0-4FA4-9F33-31A5587D325C}" name="Average" dataDxfId="0">
       <calculatedColumnFormula>AVERAGE(Table2[[#This Row],[4000]:[12000]])</calculatedColumnFormula>
     </tableColumn>
@@ -514,17 +515,17 @@
         <v>0</v>
       </c>
       <c r="B2" s="1">
-        <v>0.754</v>
+        <v>0.77200000000000002</v>
       </c>
       <c r="C2" s="1">
-        <v>0.78200000000000003</v>
+        <v>0.75700000000000001</v>
       </c>
       <c r="D2" s="1">
-        <v>0.77</v>
+        <v>0.81299999999999994</v>
       </c>
       <c r="E2" s="1">
         <f>AVERAGE(Table2[[#This Row],[4000]:[12000]])</f>
-        <v>0.76866666666666672</v>
+        <v>0.78066666666666651</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -532,17 +533,17 @@
         <v>1</v>
       </c>
       <c r="B3" s="1">
-        <v>0.92700000000000005</v>
-      </c>
-      <c r="C3" s="2">
-        <v>0.95499999999999996</v>
-      </c>
-      <c r="D3" s="1">
-        <v>0.96199999999999997</v>
+        <v>0.94</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.96</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0.96799999999999997</v>
       </c>
       <c r="E3" s="1">
         <f>AVERAGE(Table2[[#This Row],[4000]:[12000]])</f>
-        <v>0.94800000000000006</v>
+        <v>0.95599999999999996</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -567,18 +568,18 @@
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="2">
-        <v>0.94299999999999995</v>
+      <c r="B5" s="4">
+        <v>0.93100000000000005</v>
       </c>
       <c r="C5" s="1">
-        <v>0.95199999999999996</v>
+        <v>0.96699999999999997</v>
       </c>
       <c r="D5" s="2">
-        <v>0.96799999999999997</v>
+        <v>0.97199999999999998</v>
       </c>
       <c r="E5" s="2">
         <f>AVERAGE(Table2[[#This Row],[4000]:[12000]])</f>
-        <v>0.95433333333333337</v>
+        <v>0.95666666666666667</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -587,15 +588,15 @@
       </c>
       <c r="B6" s="1">
         <f>AVERAGE(B2:B5)</f>
-        <v>0.85500000000000009</v>
+        <v>0.85975000000000001</v>
       </c>
       <c r="C6" s="1">
         <f>AVERAGE(C2:C5)</f>
-        <v>0.872</v>
+        <v>0.87075000000000002</v>
       </c>
       <c r="D6" s="2">
         <f>AVERAGE(D2:D5)</f>
-        <v>0.89975000000000005</v>
+        <v>0.91299999999999992</v>
       </c>
       <c r="E6" s="1"/>
     </row>

--- a/Results.xlsx
+++ b/Results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\work\gender classification\Neural-Networks-and-Deep-Learning-Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{418D2A24-AFD9-43B2-A822-1109DD57565A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F3B0B05-6D10-4C5B-9BCA-D9AB373AFE07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{443E6BF5-3B8D-4A17-A50D-7ACF8BB371E2}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
   <si>
     <t>ViT</t>
   </si>
@@ -63,13 +63,19 @@
   </si>
   <si>
     <t>Average</t>
+  </si>
+  <si>
+    <t>Swin V2</t>
+  </si>
+  <si>
+    <t>Swin V2 (finetune)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -87,6 +93,14 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -112,12 +126,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -154,8 +169,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F5EAEC6E-5447-4E36-8D59-42E3E6DAA083}" name="Table2" displayName="Table2" ref="A1:E6" totalsRowShown="0">
-  <autoFilter ref="A1:E6" xr:uid="{F5EAEC6E-5447-4E36-8D59-42E3E6DAA083}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F5EAEC6E-5447-4E36-8D59-42E3E6DAA083}" name="Table2" displayName="Table2" ref="A1:E8" totalsRowShown="0">
+  <autoFilter ref="A1:E8" xr:uid="{F5EAEC6E-5447-4E36-8D59-42E3E6DAA083}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{4DADEE15-8A9C-4261-AFBB-FCC237FBFF32}" name="Model\Training data size" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{2CDC2B5A-DEA7-4603-8850-3897F2CDF776}" name="4000" dataDxfId="3"/>
@@ -486,7 +501,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E38132D-85C8-4537-B276-E0D44FA3F383}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.85546875" customWidth="1"/>
@@ -535,10 +550,10 @@
       <c r="B3" s="1">
         <v>0.94</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="1">
         <v>0.96</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="4">
         <v>0.96799999999999997</v>
       </c>
       <c r="E3" s="1">
@@ -568,37 +583,73 @@
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="1">
         <v>0.93100000000000005</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="5">
         <v>0.96699999999999997</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="4">
         <v>0.97199999999999998</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="4">
         <f>AVERAGE(Table2[[#This Row],[4000]:[12000]])</f>
         <v>0.95666666666666667</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="1">
+        <v>0.504</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0.84699999999999998</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0.57399999999999995</v>
+      </c>
+      <c r="E6" s="4">
+        <f>AVERAGE(Table2[[#This Row],[4000]:[12000]])</f>
+        <v>0.64166666666666661</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="5">
+        <v>0.94899999999999995</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0.96199999999999997</v>
+      </c>
+      <c r="D7" s="5">
+        <v>0.97299999999999998</v>
+      </c>
+      <c r="E7" s="2">
+        <f>AVERAGE(Table2[[#This Row],[4000]:[12000]])</f>
+        <v>0.96133333333333326</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B8" s="1">
         <f>AVERAGE(B2:B5)</f>
         <v>0.85975000000000001</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C8" s="1">
         <f>AVERAGE(C2:C5)</f>
         <v>0.87075000000000002</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D8" s="2">
         <f>AVERAGE(D2:D5)</f>
         <v>0.91299999999999992</v>
       </c>
-      <c r="E6" s="1"/>
+      <c r="E8" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Results.xlsx
+++ b/Results.xlsx
@@ -8,14 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\work\gender classification\Neural-Networks-and-Deep-Learning-Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F3B0B05-6D10-4C5B-9BCA-D9AB373AFE07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FB02350-E053-40AD-B19F-15586022B179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{443E6BF5-3B8D-4A17-A50D-7ACF8BB371E2}"/>
+    <workbookView xWindow="6825" yWindow="4515" windowWidth="28800" windowHeight="15345" xr2:uid="{443E6BF5-3B8D-4A17-A50D-7ACF8BB371E2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="0" r:id="rId4"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,18 +41,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="25">
   <si>
     <t>ViT</t>
   </si>
   <si>
-    <t>ViT (finetune)</t>
-  </si>
-  <si>
     <t>CvT</t>
-  </si>
-  <si>
-    <t>CvT (finetune)</t>
   </si>
   <si>
     <t>Model\Training data size</t>
@@ -68,14 +67,62 @@
     <t>Swin V2</t>
   </si>
   <si>
-    <t>Swin V2 (finetune)</t>
+    <t>ResNet</t>
+  </si>
+  <si>
+    <t>ResNet (fine-tune)</t>
+  </si>
+  <si>
+    <t>ViT (fine-tune)</t>
+  </si>
+  <si>
+    <t>CvT (fine-tune)</t>
+  </si>
+  <si>
+    <t>Swin V2 (fine-tune)</t>
+  </si>
+  <si>
+    <t>InceptionV3</t>
+  </si>
+  <si>
+    <t>InceptionV3 (fine-tune)</t>
+  </si>
+  <si>
+    <t>EfficientNetV2</t>
+  </si>
+  <si>
+    <t>EfficientNetV2 (fine-tune)</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Sum of 4000</t>
+  </si>
+  <si>
+    <t>Sum of 8000</t>
+  </si>
+  <si>
+    <t>Sum of 12000</t>
+  </si>
+  <si>
+    <t>SwinV2 (fine-tune)</t>
+  </si>
+  <si>
+    <t>SwinV2</t>
+  </si>
+  <si>
+    <t>EfficientNetV2 (fine-tune) trained on gender</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -105,6 +152,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="4" tint="-0.249977111117893"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="4" tint="-0.249977111117893"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -114,7 +176,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -122,33 +184,210 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="14">
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="4" tint="-0.249977111117893"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="4" tint="-0.249977111117893"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="4" tint="-0.249977111117893"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="4" tint="-0.249977111117893"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="4" tint="-0.249977111117893"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="4" tint="-0.249977111117893"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="4" tint="-0.249977111117893"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+      </border>
     </dxf>
     <dxf>
       <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -168,16 +407,8065 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-SG" sz="1800"/>
+              <a:t>Accuracy of</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-SG" sz="1800" baseline="0"/>
+              <a:t> fine-tuned models across data sizes</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-SG" sz="1800"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-SG"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ResNet (fine-tune)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$B$1:$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>4000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>12000</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$3:$D$3</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.95299999999999996</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.96799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.97299999999999998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-BA3C-4867-A9E8-1601B1284173}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>InceptionV3 (fine-tune)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$B$1:$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>4000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>12000</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$5:$D$5</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.97099999999999997</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.97599999999999998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-BA3C-4867-A9E8-1601B1284173}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>EfficientNetV2 (fine-tune)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$B$1:$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>4000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>12000</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$7:$D$7</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.97299999999999998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.98</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-BA3C-4867-A9E8-1601B1284173}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ViT (fine-tune)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$B$1:$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>4000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>12000</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$9:$D$9</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.94</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.96799999999999997</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-BA3C-4867-A9E8-1601B1284173}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="9"/>
+          <c:order val="9"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>CvT (fine-tune)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$B$1:$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>4000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>12000</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$11:$D$11</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.93100000000000005</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.96699999999999997</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.97199999999999998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000A-BA3C-4867-A9E8-1601B1284173}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="11"/>
+          <c:order val="11"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$A$13</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>SwinV2 (fine-tune)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent6">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$B$1:$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>4000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>12000</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$13:$D$13</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.94899999999999995</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.96199999999999997</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.97299999999999998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000C-BA3C-4867-A9E8-1601B1284173}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="277368527"/>
+        <c:axId val="277375727"/>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="0"/>
+                <c:order val="0"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$A$2</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>ResNet</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="28575" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent1"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent1"/>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent1"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:cat>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$B$1:$D$1</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="3"/>
+                      <c:pt idx="0">
+                        <c:v>4000</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>8000</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>12000</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$B$2:$D$2</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>0.00%</c:formatCode>
+                      <c:ptCount val="3"/>
+                      <c:pt idx="0">
+                        <c:v>0.82299999999999995</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>0.90200000000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>0.91300000000000003</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000000-BA3C-4867-A9E8-1601B1284173}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="2"/>
+                <c:order val="2"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$A$4</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>InceptionV3</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="28575" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent3"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent3"/>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent3"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:cat>
+                  <c:strRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$B$1:$D$1</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="3"/>
+                      <c:pt idx="0">
+                        <c:v>4000</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>8000</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>12000</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$B$4:$D$4</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>0.00%</c:formatCode>
+                      <c:ptCount val="3"/>
+                      <c:pt idx="0">
+                        <c:v>0.78100000000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>0.88200000000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>0.89700000000000002</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000002-BA3C-4867-A9E8-1601B1284173}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="4"/>
+                <c:order val="4"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$A$6</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>EfficientNetV2</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="28575" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent5"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent5"/>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent5"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:cat>
+                  <c:strRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$B$1:$D$1</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="3"/>
+                      <c:pt idx="0">
+                        <c:v>4000</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>8000</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>12000</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$B$6:$D$6</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>0.00%</c:formatCode>
+                      <c:ptCount val="3"/>
+                      <c:pt idx="0">
+                        <c:v>0.56699999999999995</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>0.80300000000000005</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>0.92800000000000005</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000004-BA3C-4867-A9E8-1601B1284173}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="6"/>
+                <c:order val="6"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$A$8</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>ViT</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="28575" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent1">
+                        <a:lumMod val="60000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent1">
+                        <a:lumMod val="60000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent1">
+                          <a:lumMod val="60000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:cat>
+                  <c:strRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$B$1:$D$1</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="3"/>
+                      <c:pt idx="0">
+                        <c:v>4000</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>8000</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>12000</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$B$8:$D$8</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>0.00%</c:formatCode>
+                      <c:ptCount val="3"/>
+                      <c:pt idx="0">
+                        <c:v>0.77200000000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>0.75700000000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>0.81299999999999994</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000007-BA3C-4867-A9E8-1601B1284173}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="8"/>
+                <c:order val="8"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$A$10</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>CvT</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="28575" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent3">
+                        <a:lumMod val="60000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent3">
+                        <a:lumMod val="60000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent3">
+                          <a:lumMod val="60000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:cat>
+                  <c:strRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$B$1:$D$1</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="3"/>
+                      <c:pt idx="0">
+                        <c:v>4000</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>8000</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>12000</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$B$10:$D$10</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>0.00%</c:formatCode>
+                      <c:ptCount val="3"/>
+                      <c:pt idx="0">
+                        <c:v>0.79600000000000004</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>0.79900000000000004</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>0.89900000000000002</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000009-BA3C-4867-A9E8-1601B1284173}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="10"/>
+                <c:order val="10"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$A$12</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>SwinV2</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="28575" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent5">
+                        <a:lumMod val="60000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent5">
+                        <a:lumMod val="60000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent5">
+                          <a:lumMod val="60000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:cat>
+                  <c:strRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$B$1:$D$1</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="3"/>
+                      <c:pt idx="0">
+                        <c:v>4000</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>8000</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>12000</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$B$12:$D$12</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>0.00%</c:formatCode>
+                      <c:ptCount val="3"/>
+                      <c:pt idx="0">
+                        <c:v>0.504</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>0.84699999999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>0.57399999999999995</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{0000000B-BA3C-4867-A9E8-1601B1284173}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+          </c:ext>
+        </c:extLst>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="277368527"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="277375727"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="277375727"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1"/>
+          <c:min val="0.9"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="277368527"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Accuracy of models across</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> data sizes</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>4000</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$2:$A$13</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>ResNet</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ResNet (fine-tune)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>InceptionV3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>InceptionV3 (fine-tune)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>EfficientNetV2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>EfficientNetV2 (fine-tune)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>ViT</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>ViT (fine-tune)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>CvT</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>CvT (fine-tune)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>SwinV2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>SwinV2 (fine-tune)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$2:$B$13</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.82299999999999995</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.95299999999999996</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.78100000000000003</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.56699999999999995</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.77200000000000002</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.94</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.79600000000000004</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.93100000000000005</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.504</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.94899999999999995</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5161-4A6A-8B9C-9F22F155504D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>8000</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$2:$A$13</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>ResNet</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ResNet (fine-tune)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>InceptionV3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>InceptionV3 (fine-tune)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>EfficientNetV2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>EfficientNetV2 (fine-tune)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>ViT</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>ViT (fine-tune)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>CvT</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>CvT (fine-tune)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>SwinV2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>SwinV2 (fine-tune)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$2:$C$13</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.90200000000000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.96799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.88200000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.97099999999999997</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.80300000000000005</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.97299999999999998</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.75700000000000001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.79900000000000004</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.96699999999999997</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.84699999999999998</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.96199999999999997</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-5161-4A6A-8B9C-9F22F155504D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>12000</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$2:$A$13</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>ResNet</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ResNet (fine-tune)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>InceptionV3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>InceptionV3 (fine-tune)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>EfficientNetV2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>EfficientNetV2 (fine-tune)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>ViT</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>ViT (fine-tune)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>CvT</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>CvT (fine-tune)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>SwinV2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>SwinV2 (fine-tune)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$2:$D$13</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.91300000000000003</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.97299999999999998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.89700000000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.97599999999999998</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.92800000000000005</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.98</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.81299999999999994</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.96799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.89900000000000002</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.97199999999999998</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.57399999999999995</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.97299999999999998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-5161-4A6A-8B9C-9F22F155504D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="277399727"/>
+        <c:axId val="277396847"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="277399727"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="277396847"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="277396847"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1"/>
+          <c:min val="0.5"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="277399727"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-SG" sz="1600"/>
+              <a:t>Accuracy of</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-SG" sz="1600" baseline="0"/>
+              <a:t> models trained from scratch across data sizes</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-SG" sz="1600"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-SG"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ResNet</c:v>
+                </c:pt>
+              </c:strCache>
+              <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"/>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$B$1:$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>4000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>12000</c:v>
+                </c:pt>
+              </c:strCache>
+              <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"/>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$2:$D$2</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.82299999999999995</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.90200000000000002</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.91300000000000003</c:v>
+                </c:pt>
+              </c:numCache>
+              <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-03F8-41D8-8385-F19221234BD9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>InceptionV3</c:v>
+                </c:pt>
+              </c:strCache>
+              <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"/>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$B$1:$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>4000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>12000</c:v>
+                </c:pt>
+              </c:strCache>
+              <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"/>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$4:$D$4</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.78100000000000003</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.88200000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.89700000000000002</c:v>
+                </c:pt>
+              </c:numCache>
+              <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-03F8-41D8-8385-F19221234BD9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>EfficientNetV2</c:v>
+                </c:pt>
+              </c:strCache>
+              <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"/>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$B$1:$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>4000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>12000</c:v>
+                </c:pt>
+              </c:strCache>
+              <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"/>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$6:$D$6</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.56699999999999995</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.80300000000000005</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.92800000000000005</c:v>
+                </c:pt>
+              </c:numCache>
+              <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-03F8-41D8-8385-F19221234BD9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ViT</c:v>
+                </c:pt>
+              </c:strCache>
+              <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"/>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$B$1:$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>4000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>12000</c:v>
+                </c:pt>
+              </c:strCache>
+              <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"/>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$8:$D$8</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.77200000000000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.75700000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.81299999999999994</c:v>
+                </c:pt>
+              </c:numCache>
+              <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000009-03F8-41D8-8385-F19221234BD9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="8"/>
+          <c:order val="8"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>CvT</c:v>
+                </c:pt>
+              </c:strCache>
+              <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"/>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$B$1:$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>4000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>12000</c:v>
+                </c:pt>
+              </c:strCache>
+              <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"/>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$10:$D$10</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.79600000000000004</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.79900000000000004</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.89900000000000002</c:v>
+                </c:pt>
+              </c:numCache>
+              <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000A-03F8-41D8-8385-F19221234BD9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="10"/>
+          <c:order val="10"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$A$12</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>SwinV2</c:v>
+                </c:pt>
+              </c:strCache>
+              <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"/>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$B$1:$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>4000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>12000</c:v>
+                </c:pt>
+              </c:strCache>
+              <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"/>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$12:$D$12</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.504</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.84699999999999998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.57399999999999995</c:v>
+                </c:pt>
+              </c:numCache>
+              <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000B-03F8-41D8-8385-F19221234BD9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="277368527"/>
+        <c:axId val="277375727"/>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="1"/>
+                <c:order val="1"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$A$3</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>ResNet (fine-tune)</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="28575" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent2"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent2"/>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent2"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:cat>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$B$1:$D$1</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="3"/>
+                      <c:pt idx="0">
+                        <c:v>4000</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>8000</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>12000</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$B$3:$D$3</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>0.00%</c:formatCode>
+                      <c:ptCount val="3"/>
+                      <c:pt idx="0">
+                        <c:v>0.95299999999999996</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>0.96799999999999997</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>0.97299999999999998</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000000-03F8-41D8-8385-F19221234BD9}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="3"/>
+                <c:order val="3"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$A$5</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>InceptionV3 (fine-tune)</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="28575" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent4"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent4"/>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent4"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:cat>
+                  <c:strRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$B$1:$D$1</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="3"/>
+                      <c:pt idx="0">
+                        <c:v>4000</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>8000</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>12000</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$B$5:$D$5</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>0.00%</c:formatCode>
+                      <c:ptCount val="3"/>
+                      <c:pt idx="0">
+                        <c:v>0.95</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>0.97099999999999997</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>0.97599999999999998</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000001-03F8-41D8-8385-F19221234BD9}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="5"/>
+                <c:order val="5"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$A$7</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>EfficientNetV2 (fine-tune)</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="28575" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent6"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent6"/>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent6"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:cat>
+                  <c:strRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$B$1:$D$1</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="3"/>
+                      <c:pt idx="0">
+                        <c:v>4000</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>8000</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>12000</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$B$7:$D$7</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>0.00%</c:formatCode>
+                      <c:ptCount val="3"/>
+                      <c:pt idx="0">
+                        <c:v>0.96</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>0.97299999999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>0.98</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000002-03F8-41D8-8385-F19221234BD9}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="7"/>
+                <c:order val="7"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$A$9</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>ViT (fine-tune)</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="28575" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent2">
+                        <a:lumMod val="60000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent2">
+                        <a:lumMod val="60000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent2">
+                          <a:lumMod val="60000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:cat>
+                  <c:strRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$B$1:$D$1</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="3"/>
+                      <c:pt idx="0">
+                        <c:v>4000</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>8000</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>12000</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$B$9:$D$9</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>0.00%</c:formatCode>
+                      <c:ptCount val="3"/>
+                      <c:pt idx="0">
+                        <c:v>0.94</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>0.96</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>0.96799999999999997</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000003-03F8-41D8-8385-F19221234BD9}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="9"/>
+                <c:order val="9"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$A$11</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>CvT (fine-tune)</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="28575" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent4">
+                        <a:lumMod val="60000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent4">
+                        <a:lumMod val="60000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent4">
+                          <a:lumMod val="60000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:cat>
+                  <c:strRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$B$1:$D$1</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="3"/>
+                      <c:pt idx="0">
+                        <c:v>4000</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>8000</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>12000</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$B$11:$D$11</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>0.00%</c:formatCode>
+                      <c:ptCount val="3"/>
+                      <c:pt idx="0">
+                        <c:v>0.93100000000000005</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>0.96699999999999997</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>0.97199999999999998</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000004-03F8-41D8-8385-F19221234BD9}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="11"/>
+                <c:order val="11"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$A$13</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>SwinV2 (fine-tune)</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="28575" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent6">
+                        <a:lumMod val="60000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent6">
+                        <a:lumMod val="60000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent6">
+                          <a:lumMod val="60000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:cat>
+                  <c:strRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$B$1:$D$1</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="3"/>
+                      <c:pt idx="0">
+                        <c:v>4000</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>8000</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>12000</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$B$13:$D$13</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>0.00%</c:formatCode>
+                      <c:ptCount val="3"/>
+                      <c:pt idx="0">
+                        <c:v>0.94899999999999995</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>0.96199999999999997</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>0.97299999999999998</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000005-03F8-41D8-8385-F19221234BD9}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+          </c:ext>
+        </c:extLst>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="277368527"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="277375727"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="277375727"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1"/>
+          <c:min val="0.5"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="277368527"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Results.xlsx]Sheet2!PivotTable1</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$D$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Sum of 4000</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet2!$C$4:$C$16</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>CvT</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>CvT (fine-tune)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>EfficientNetV2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>EfficientNetV2 (fine-tune)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>InceptionV3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>InceptionV3 (fine-tune)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>ResNet</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>ResNet (fine-tune)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Swin V2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Swin V2 (fine-tune)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>ViT</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>ViT (fine-tune)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$D$4:$D$16</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.79600000000000004</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.93100000000000005</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.55400000000000005</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.78100000000000003</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.82299999999999995</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.95299999999999996</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.504</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.94899999999999995</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.77200000000000002</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.94</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A352-446E-9795-A3CD2889D598}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$E$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Sum of 8000</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet2!$C$4:$C$16</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>CvT</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>CvT (fine-tune)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>EfficientNetV2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>EfficientNetV2 (fine-tune)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>InceptionV3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>InceptionV3 (fine-tune)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>ResNet</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>ResNet (fine-tune)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Swin V2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Swin V2 (fine-tune)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>ViT</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>ViT (fine-tune)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$E$4:$E$16</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.79900000000000004</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.96699999999999997</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.80300000000000005</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.97299999999999998</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.88200000000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.97099999999999997</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.90200000000000002</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.96799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.84699999999999998</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.96199999999999997</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.75700000000000001</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.96</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-A352-446E-9795-A3CD2889D598}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$F$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Sum of 12000</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet2!$C$4:$C$16</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>CvT</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>CvT (fine-tune)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>EfficientNetV2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>EfficientNetV2 (fine-tune)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>InceptionV3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>InceptionV3 (fine-tune)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>ResNet</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>ResNet (fine-tune)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Swin V2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Swin V2 (fine-tune)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>ViT</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>ViT (fine-tune)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$F$4:$F$16</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.89900000000000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.97199999999999998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.497</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.79300000000000004</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.89700000000000002</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.97599999999999998</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.91300000000000003</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.97299999999999998</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.57399999999999995</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.97299999999999998</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.81299999999999994</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.96799999999999997</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-A352-446E-9795-A3CD2889D598}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1707324383"/>
+        <c:axId val="1707341183"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1707324383"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1707341183"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1707341183"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1707324383"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-SG"/>
+              <a:t>Accuracy across datasizes and model</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-SG" baseline="0"/>
+              <a:t>s</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-SG"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-SG"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>4000</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$2:$A$13</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>ResNet</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ResNet (fine-tune)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>InceptionV3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>InceptionV3 (fine-tune)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>EfficientNetV2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>EfficientNetV2 (fine-tune)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>ViT</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>ViT (fine-tune)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>CvT</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>CvT (fine-tune)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>SwinV2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>SwinV2 (fine-tune)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$2:$B$13</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.82299999999999995</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.95299999999999996</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.78100000000000003</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.56699999999999995</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.77200000000000002</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.94</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.79600000000000004</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.93100000000000005</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.504</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.94899999999999995</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-21D5-4990-95B7-D1894238B238}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>8000</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$2:$A$13</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>ResNet</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ResNet (fine-tune)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>InceptionV3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>InceptionV3 (fine-tune)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>EfficientNetV2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>EfficientNetV2 (fine-tune)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>ViT</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>ViT (fine-tune)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>CvT</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>CvT (fine-tune)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>SwinV2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>SwinV2 (fine-tune)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$2:$C$13</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.90200000000000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.96799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.88200000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.97099999999999997</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.80300000000000005</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.97299999999999998</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.75700000000000001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.79900000000000004</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.96699999999999997</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.84699999999999998</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.96199999999999997</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-21D5-4990-95B7-D1894238B238}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>12000</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$2:$A$13</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>ResNet</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ResNet (fine-tune)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>InceptionV3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>InceptionV3 (fine-tune)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>EfficientNetV2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>EfficientNetV2 (fine-tune)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>ViT</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>ViT (fine-tune)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>CvT</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>CvT (fine-tune)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>SwinV2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>SwinV2 (fine-tune)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$2:$D$13</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.91300000000000003</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.97299999999999998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.89700000000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.97599999999999998</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.92800000000000005</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.98</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.81299999999999994</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.96799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.89900000000000002</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.97199999999999998</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.57399999999999995</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.97299999999999998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-21D5-4990-95B7-D1894238B238}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="140260623"/>
+        <c:axId val="140259183"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="140260623"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="140259183"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="140259183"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="140260623"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>89649</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>77881</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>280147</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>11206</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EAD17CCF-C689-1010-2960-56B7D2D8D38E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1160645</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>22412</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>324970</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>68634</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E89F2B9D-CEC8-7946-E69B-E9774947C0AC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>280148</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>33617</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>470646</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>157442</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Chart 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C746CBD-534E-409C-B3FE-09BE5DF982B8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>587595</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>177526</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>282795</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>63226</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A9987867-9E15-3237-A4CD-C1F558CAA2DE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>447260</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>57977</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>538369</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>182216</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C6742726-FDD0-432C-933A-54BB193E007C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Wong Wai Hoe" refreshedDate="45757.467229050926" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="12" xr:uid="{EDAD6B99-FD98-43C2-95CF-6EECCE4C460E}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:D13" sheet="Sheet1"/>
+  </cacheSource>
+  <cacheFields count="4">
+    <cacheField name="Model\Training data size" numFmtId="0">
+      <sharedItems count="12">
+        <s v="ResNet"/>
+        <s v="ResNet (fine-tune)"/>
+        <s v="InceptionV3"/>
+        <s v="InceptionV3 (fine-tune)"/>
+        <s v="EfficientNetV2"/>
+        <s v="EfficientNetV2 (fine-tune)"/>
+        <s v="ViT"/>
+        <s v="ViT (fine-tune)"/>
+        <s v="CvT"/>
+        <s v="CvT (fine-tune)"/>
+        <s v="Swin V2"/>
+        <s v="Swin V2 (fine-tune)"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="4000" numFmtId="10">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.504" maxValue="0.96"/>
+    </cacheField>
+    <cacheField name="8000" numFmtId="10">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.75700000000000001" maxValue="0.97299999999999998"/>
+    </cacheField>
+    <cacheField name="12000" numFmtId="10">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.497" maxValue="0.97599999999999998"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="12">
+  <r>
+    <x v="0"/>
+    <n v="0.82299999999999995"/>
+    <n v="0.90200000000000002"/>
+    <n v="0.91300000000000003"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="0.95299999999999996"/>
+    <n v="0.96799999999999997"/>
+    <n v="0.97299999999999998"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="0.78100000000000003"/>
+    <n v="0.88200000000000001"/>
+    <n v="0.89700000000000002"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="0.95"/>
+    <n v="0.97099999999999997"/>
+    <n v="0.97599999999999998"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="0.55400000000000005"/>
+    <n v="0.80300000000000005"/>
+    <n v="0.497"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <n v="0.96"/>
+    <n v="0.97299999999999998"/>
+    <n v="0.79300000000000004"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <n v="0.77200000000000002"/>
+    <n v="0.75700000000000001"/>
+    <n v="0.81299999999999994"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <n v="0.94"/>
+    <n v="0.96"/>
+    <n v="0.96799999999999997"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <n v="0.79600000000000004"/>
+    <n v="0.79900000000000004"/>
+    <n v="0.89900000000000002"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <n v="0.93100000000000005"/>
+    <n v="0.96699999999999997"/>
+    <n v="0.97199999999999998"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <n v="0.504"/>
+    <n v="0.84699999999999998"/>
+    <n v="0.57399999999999995"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <n v="0.94899999999999995"/>
+    <n v="0.96199999999999997"/>
+    <n v="0.97299999999999998"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{69343F57-C725-4267-AEEA-9326996DC700}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0" chartFormat="1">
+  <location ref="C3:F16" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="4">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="13">
+        <item x="8"/>
+        <item x="9"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" numFmtId="10" showAll="0"/>
+    <pivotField dataField="1" numFmtId="10" showAll="0"/>
+    <pivotField dataField="1" numFmtId="10" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="13">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+  </colItems>
+  <dataFields count="3">
+    <dataField name="Sum of 4000" fld="1" baseField="0" baseItem="0" numFmtId="10"/>
+    <dataField name="Sum of 8000" fld="2" baseField="0" baseItem="0" numFmtId="10"/>
+    <dataField name="Sum of 12000" fld="3" baseField="0" baseItem="0" numFmtId="10"/>
+  </dataFields>
+  <chartFormats count="3">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F5EAEC6E-5447-4E36-8D59-42E3E6DAA083}" name="Table2" displayName="Table2" ref="A1:E8" totalsRowShown="0">
-  <autoFilter ref="A1:E8" xr:uid="{F5EAEC6E-5447-4E36-8D59-42E3E6DAA083}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F5EAEC6E-5447-4E36-8D59-42E3E6DAA083}" name="Table2" displayName="Table2" ref="A1:E14" totalsRowShown="0">
+  <autoFilter ref="A1:E14" xr:uid="{F5EAEC6E-5447-4E36-8D59-42E3E6DAA083}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{4DADEE15-8A9C-4261-AFBB-FCC237FBFF32}" name="Model\Training data size" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{2CDC2B5A-DEA7-4603-8850-3897F2CDF776}" name="4000" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{5060743F-C095-4F0A-96EC-4EF75F791B0C}" name="8000" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{2F8F5957-488C-4C0E-BA55-0DA7501484F9}" name="12000" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{E0A3210C-CFA0-4FA4-9F33-31A5587D325C}" name="Average" dataDxfId="0">
+    <tableColumn id="1" xr3:uid="{4DADEE15-8A9C-4261-AFBB-FCC237FBFF32}" name="Model\Training data size" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{2CDC2B5A-DEA7-4603-8850-3897F2CDF776}" name="4000" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{5060743F-C095-4F0A-96EC-4EF75F791B0C}" name="8000" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{2F8F5957-488C-4C0E-BA55-0DA7501484F9}" name="12000" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{E0A3210C-CFA0-4FA4-9F33-31A5587D325C}" name="Average" dataDxfId="9">
       <calculatedColumnFormula>AVERAGE(Table2[[#This Row],[4000]:[12000]])</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00584167-E8B8-4688-AA9F-A38E7C81738C}" name="Table1" displayName="Table1" ref="A1:E3" totalsRowShown="0" headerRowDxfId="1" dataDxfId="2" headerRowBorderDxfId="7" tableBorderDxfId="8">
+  <autoFilter ref="A1:E3" xr:uid="{00584167-E8B8-4688-AA9F-A38E7C81738C}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{7517984C-FBD6-4098-B6BC-AD0C2141CEA1}" name="Model\Training data size" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{F6F5F28E-8E2E-4C1C-AB6F-B9652822A90B}" name="4000" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{B7126FF2-A512-473B-9814-9AB6075BC78B}" name="8000" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{04D568F7-6F94-4148-AC2E-ED1510ED4210}" name="12000" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{A1C62948-0A19-4A9F-BAF7-7B448793D1B9}" name="Average" dataDxfId="0">
+      <calculatedColumnFormula>AVERAGE(Table1[[#This Row],[4000]:[12000]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -501,7 +8789,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E38132D-85C8-4537-B276-E0D44FA3F383}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.85546875" customWidth="1"/>
@@ -510,152 +8798,545 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>6</v>
-      </c>
-      <c r="D1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="3">
+        <v>0.82299999999999995</v>
+      </c>
+      <c r="C2" s="3">
+        <v>0.90200000000000002</v>
+      </c>
+      <c r="D2" s="3">
+        <v>0.91300000000000003</v>
+      </c>
+      <c r="E2" s="3">
+        <f>AVERAGE(Table2[[#This Row],[4000]:[12000]])</f>
+        <v>0.8793333333333333</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="3">
+        <v>0.95299999999999996</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0.96799999999999997</v>
+      </c>
+      <c r="D3" s="3">
+        <v>0.97299999999999998</v>
+      </c>
+      <c r="E3" s="3">
+        <f>AVERAGE(Table2[[#This Row],[4000]:[12000]])</f>
+        <v>0.96466666666666656</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="3">
+        <v>0.78100000000000003</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0.88200000000000001</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0.89700000000000002</v>
+      </c>
+      <c r="E4" s="3">
+        <f>AVERAGE(Table2[[#This Row],[4000]:[12000]])</f>
+        <v>0.85333333333333339</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0.97099999999999997</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0.97599999999999998</v>
+      </c>
+      <c r="E5" s="3">
+        <f>AVERAGE(Table2[[#This Row],[4000]:[12000]])</f>
+        <v>0.96566666666666656</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="3">
+        <v>0.56699999999999995</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0.80300000000000005</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0.92800000000000005</v>
+      </c>
+      <c r="E6" s="3">
+        <f>AVERAGE(Table2[[#This Row],[4000]:[12000]])</f>
+        <v>0.76600000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="3">
+        <v>0.96</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0.97299999999999998</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0.98</v>
+      </c>
+      <c r="E7" s="3">
+        <f>AVERAGE(Table2[[#This Row],[4000]:[12000]])</f>
+        <v>0.97099999999999997</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B8" s="3">
         <v>0.77200000000000002</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C8" s="3">
         <v>0.75700000000000001</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D8" s="3">
         <v>0.81299999999999994</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E8" s="3">
         <f>AVERAGE(Table2[[#This Row],[4000]:[12000]])</f>
         <v>0.78066666666666651</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="3">
         <v>0.94</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C9" s="3">
         <v>0.96</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D9" s="3">
         <v>0.96799999999999997</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E9" s="3">
         <f>AVERAGE(Table2[[#This Row],[4000]:[12000]])</f>
         <v>0.95599999999999996</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="1">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="3">
         <v>0.79600000000000004</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C10" s="3">
         <v>0.79900000000000004</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D10" s="3">
         <v>0.89900000000000002</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E10" s="3">
         <f>AVERAGE(Table2[[#This Row],[4000]:[12000]])</f>
         <v>0.83133333333333337</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="3">
         <v>0.93100000000000005</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C11" s="4">
         <v>0.96699999999999997</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D11" s="3">
         <v>0.97199999999999998</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E11" s="3">
         <f>AVERAGE(Table2[[#This Row],[4000]:[12000]])</f>
         <v>0.95666666666666667</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="1">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="3">
         <v>0.504</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C12" s="3">
         <v>0.84699999999999998</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D12" s="3">
         <v>0.57399999999999995</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E12" s="3">
         <f>AVERAGE(Table2[[#This Row],[4000]:[12000]])</f>
         <v>0.64166666666666661</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="4">
         <v>0.94899999999999995</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C13" s="3">
         <v>0.96199999999999997</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D13" s="4">
         <v>0.97299999999999998</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E13" s="5">
         <f>AVERAGE(Table2[[#This Row],[4000]:[12000]])</f>
         <v>0.96133333333333326</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="1">
-        <f>AVERAGE(B2:B5)</f>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="3">
+        <f>AVERAGE(B8:B11)</f>
         <v>0.85975000000000001</v>
       </c>
-      <c r="C8" s="1">
-        <f>AVERAGE(C2:C5)</f>
+      <c r="C14" s="3">
+        <f>AVERAGE(C8:C11)</f>
         <v>0.87075000000000002</v>
       </c>
-      <c r="D8" s="2">
-        <f>AVERAGE(D2:D5)</f>
+      <c r="D14" s="5">
+        <f>AVERAGE(D8:D11)</f>
         <v>0.91299999999999992</v>
       </c>
-      <c r="E8" s="1"/>
+      <c r="E14" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AB8C45F-A386-4EDA-9310-2A348E7CEB45}">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="41.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="3">
+        <v>0.96</v>
+      </c>
+      <c r="C2" s="3">
+        <v>0.97299999999999998</v>
+      </c>
+      <c r="D2" s="3">
+        <v>0.98</v>
+      </c>
+      <c r="E2" s="3">
+        <f>AVERAGE(Table1[[#This Row],[4000]:[12000]])</f>
+        <v>0.97099999999999997</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="9">
+        <v>0.97199999999999998</v>
+      </c>
+      <c r="C3" s="9">
+        <v>0.97699999999999998</v>
+      </c>
+      <c r="D3" s="9">
+        <v>0.98099999999999998</v>
+      </c>
+      <c r="E3" s="9">
+        <f>AVERAGE(Table1[[#This Row],[4000]:[12000]])</f>
+        <v>0.97666666666666657</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F8641C8-98F9-4E7E-AFD1-D4810AB8AD9A}">
+  <dimension ref="C3:F16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C4" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0.79600000000000004</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0.79900000000000004</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0.89900000000000002</v>
+      </c>
+    </row>
+    <row r="5" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0.93100000000000005</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0.96699999999999997</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0.97199999999999998</v>
+      </c>
+    </row>
+    <row r="6" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C6" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0.55400000000000005</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0.80300000000000005</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0.497</v>
+      </c>
+    </row>
+    <row r="7" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C7" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0.96</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0.97299999999999998</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0.79300000000000004</v>
+      </c>
+    </row>
+    <row r="8" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C8" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0.78100000000000003</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0.88200000000000001</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0.89700000000000002</v>
+      </c>
+    </row>
+    <row r="9" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0.95</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0.97099999999999997</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0.97599999999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C10" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0.82299999999999995</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0.90200000000000002</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0.91300000000000003</v>
+      </c>
+    </row>
+    <row r="11" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C11" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0.95299999999999996</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0.96799999999999997</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0.97299999999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C12" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0.504</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0.84699999999999998</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0.57399999999999995</v>
+      </c>
+    </row>
+    <row r="13" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C13" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="1">
+        <v>0.94899999999999995</v>
+      </c>
+      <c r="E13" s="1">
+        <v>0.96199999999999997</v>
+      </c>
+      <c r="F13" s="1">
+        <v>0.97299999999999998</v>
+      </c>
+    </row>
+    <row r="14" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C14" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D14" s="1">
+        <v>0.77200000000000002</v>
+      </c>
+      <c r="E14" s="1">
+        <v>0.75700000000000001</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0.81299999999999994</v>
+      </c>
+    </row>
+    <row r="15" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C15" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="1">
+        <v>0.94</v>
+      </c>
+      <c r="E15" s="1">
+        <v>0.96</v>
+      </c>
+      <c r="F15" s="1">
+        <v>0.96799999999999997</v>
+      </c>
+    </row>
+    <row r="16" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C16" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="1">
+        <v>9.9130000000000003</v>
+      </c>
+      <c r="E16" s="1">
+        <v>10.791</v>
+      </c>
+      <c r="F16" s="1">
+        <v>10.248000000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>